--- a/src/utils/sxsyzlzq/friends/jiaoshou/zz_js_level.xlsx
+++ b/src/utils/sxsyzlzq/friends/jiaoshou/zz_js_level.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="10725" windowHeight="11385" firstSheet="2" activeTab="1"/>
+    <workbookView windowWidth="11550" windowHeight="10425" firstSheet="2" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="帝国" sheetId="5" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="55">
   <si>
     <t>名称</t>
   </si>
@@ -43,10 +43,19 @@
     <t>圣殿斥候</t>
   </si>
   <si>
+    <t>旅行背包</t>
+  </si>
+  <si>
+    <t>圣殿卫士</t>
+  </si>
+  <si>
+    <t>民兵队长</t>
+  </si>
+  <si>
     <t>天使琼浆</t>
   </si>
   <si>
-    <t>圣殿弩手</t>
+    <t>炫目神光</t>
   </si>
   <si>
     <t>增援战线</t>
@@ -55,30 +64,30 @@
     <t>田园守望者</t>
   </si>
   <si>
+    <t>光明惩戒</t>
+  </si>
+  <si>
     <t>小计：</t>
   </si>
   <si>
     <t>蓝色卡等：</t>
   </si>
   <si>
-    <t>圣殿御卫</t>
+    <t>四芒军旗</t>
+  </si>
+  <si>
+    <t>传记·钢铁守卫</t>
   </si>
   <si>
     <t>白袍主教</t>
   </si>
   <si>
-    <t>圣殿骑士</t>
-  </si>
-  <si>
     <t>召集护卫</t>
   </si>
   <si>
     <t>紫色卡等：</t>
   </si>
   <si>
-    <t>曙光·安娜贝尔</t>
-  </si>
-  <si>
     <t>圣枪·卡洛琳</t>
   </si>
   <si>
@@ -103,61 +112,61 @@
     <t>帝国卡等：</t>
   </si>
   <si>
+    <t>洞悉之眼</t>
+  </si>
+  <si>
     <t>学仆-观测型</t>
   </si>
   <si>
     <t>沉重否定</t>
   </si>
   <si>
-    <t>灵能布控</t>
-  </si>
-  <si>
     <t>全数否定</t>
   </si>
   <si>
-    <t>占卜命运</t>
-  </si>
-  <si>
-    <t>破魔系教授</t>
+    <t>学仆-能源型</t>
+  </si>
+  <si>
+    <t>请示隐秘者</t>
   </si>
   <si>
     <t>克隆术</t>
   </si>
   <si>
-    <t>咒术系学士</t>
-  </si>
-  <si>
     <t>神秘学教授</t>
   </si>
   <si>
-    <t>幻域秘树</t>
+    <t>学仆-脉冲型</t>
   </si>
   <si>
     <t>观星台大预言家</t>
   </si>
   <si>
-    <t>米拉方舟</t>
-  </si>
-  <si>
     <t>No.2时光·米拉</t>
   </si>
   <si>
     <t>隐秘卡等：</t>
   </si>
   <si>
+    <t>长耳庄巧姑</t>
+  </si>
+  <si>
+    <t>明月心</t>
+  </si>
+  <si>
     <t>飓风术</t>
   </si>
   <si>
-    <t>太极剑法</t>
-  </si>
-  <si>
-    <t>明月心</t>
+    <t>连击</t>
+  </si>
+  <si>
+    <t>铁山靠</t>
   </si>
   <si>
     <t>明月曲</t>
   </si>
   <si>
-    <t>风卷残云</t>
+    <t>祥云师太</t>
   </si>
   <si>
     <t>墨轩隐士</t>
@@ -166,10 +175,19 @@
     <t>蟠桃会</t>
   </si>
   <si>
-    <t>萌化术</t>
+    <t>万物之灵</t>
+  </si>
+  <si>
+    <t>龟族印记</t>
   </si>
   <si>
     <t>灵龟神丹</t>
+  </si>
+  <si>
+    <t>神机玄女·轩</t>
+  </si>
+  <si>
+    <t>三熊阵</t>
   </si>
   <si>
     <t>悟能禅杖</t>
@@ -1139,7 +1157,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="16.375" customWidth="1"/>
@@ -1174,10 +1192,10 @@
         <v>4</v>
       </c>
       <c r="B3" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3" s="1">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1185,7 +1203,7 @@
         <v>5</v>
       </c>
       <c r="B4" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C4" s="1">
         <v>22</v>
@@ -1196,7 +1214,7 @@
         <v>6</v>
       </c>
       <c r="B5" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C5" s="1">
         <v>22</v>
@@ -1207,206 +1225,272 @@
         <v>7</v>
       </c>
       <c r="B6" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C6" s="1">
         <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
+      <c r="A7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="1">
+        <v>2</v>
+      </c>
+      <c r="C7" s="1">
+        <v>15</v>
+      </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-    </row>
-    <row r="9" spans="1:4">
+      <c r="A8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="1">
+        <v>2</v>
+      </c>
+      <c r="C8" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
       <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="1">
+        <v>2</v>
+      </c>
+      <c r="C9" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="1">
+        <v>2</v>
+      </c>
+      <c r="C10" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="1">
-        <f>AVERAGE(C2:C6)</f>
-        <v>21.2</v>
-      </c>
-      <c r="D9" s="2"/>
+      <c r="B11" s="1">
+        <v>3</v>
+      </c>
+      <c r="C11" s="1">
+        <v>22</v>
+      </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="2">
-        <v>2</v>
-      </c>
-      <c r="C12" s="2">
+      <c r="B12" s="1">
+        <v>3</v>
+      </c>
+      <c r="C12" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="1">
+        <v>5</v>
+      </c>
+      <c r="C13" s="1">
         <v>22</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B13" s="2">
+    <row r="14" spans="1:3">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C16" s="1">
+        <f>AVERAGE(C2:C13)</f>
+        <v>19.0833333333333</v>
+      </c>
+      <c r="D16" s="2"/>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" s="2">
+        <v>1</v>
+      </c>
+      <c r="C19" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" s="2">
+        <v>1</v>
+      </c>
+      <c r="C20" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B21" s="2">
         <v>3</v>
       </c>
-      <c r="C13" s="2">
+      <c r="C21" s="2">
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="2" t="s">
+    <row r="22" spans="1:3">
+      <c r="A22" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B22" s="2">
+        <v>4</v>
+      </c>
+      <c r="C22" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="2"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="2"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="2">
-        <v>3</v>
-      </c>
-      <c r="C14" s="2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B15" s="2">
+      <c r="B25" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C25" s="2">
+        <f>AVERAGE(C19:C22)</f>
+        <v>21.25</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B28" s="3">
         <v>4</v>
       </c>
-      <c r="C15" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C18" s="2">
-        <f>AVERAGE(C12:C15)</f>
-        <v>21.5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B21" s="3">
-        <v>3</v>
-      </c>
-      <c r="C21" s="3">
+      <c r="C28" s="3">
         <v>21</v>
       </c>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B22" s="3">
-        <v>4</v>
-      </c>
-      <c r="C22" s="3">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B23" s="3">
-        <v>4</v>
-      </c>
-      <c r="C23" s="3">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B24" s="3">
-        <v>5</v>
-      </c>
-      <c r="C24" s="3">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
-      <c r="A25" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B25" s="3">
-        <v>6</v>
-      </c>
-      <c r="C25" s="3">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B26" s="3">
-        <v>8</v>
-      </c>
-      <c r="C26" s="3">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3">
-      <c r="A27" s="3"/>
-      <c r="B27" s="3"/>
-      <c r="C27" s="3"/>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="A28" s="3"/>
-      <c r="B28" s="3"/>
-      <c r="C28" s="3"/>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B29" s="3">
+        <v>4</v>
+      </c>
+      <c r="C29" s="3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B30" s="3">
+        <v>5</v>
+      </c>
+      <c r="C30" s="3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B31" s="3">
+        <v>6</v>
+      </c>
+      <c r="C31" s="3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B32" s="3">
         <v>8</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C29" s="3">
-        <f>AVERAGE(C21:C26)</f>
+      <c r="C32" s="3">
         <v>20</v>
       </c>
     </row>
-    <row r="32" spans="1:3">
-      <c r="A32" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C32" s="4">
-        <f>AVERAGE(C2:C6,C12:C15,C21:C26)</f>
-        <v>20.8</v>
+    <row r="33" spans="1:3">
+      <c r="A33" s="3"/>
+      <c r="B33" s="3"/>
+      <c r="C33" s="3"/>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="3"/>
+      <c r="B34" s="3"/>
+      <c r="C34" s="3"/>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C35" s="3">
+        <f>AVERAGE(C28:C32)</f>
+        <v>20.6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C38" s="4">
+        <f>AVERAGE(C2:C13,C19:C22,C28:C32)</f>
+        <v>19.8571428571429</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="C9 C32" formulaRange="1"/>
+    <ignoredError sqref="C38 C16" formulaRange="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1424,40 +1508,40 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B1" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C1" s="1">
-        <v>22</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B2" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C2" s="1">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B3" s="1">
         <v>2</v>
       </c>
       <c r="C3" s="1">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B4" s="1">
         <v>2</v>
@@ -1468,110 +1552,110 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B5" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C5" s="1">
-        <v>22</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B6" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C6" s="1">
         <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
+      <c r="A7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" s="1">
+        <v>3</v>
+      </c>
+      <c r="C7" s="1">
+        <v>22</v>
+      </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-    </row>
-    <row r="9" spans="1:4">
+      <c r="A8" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" s="1">
+        <v>5</v>
+      </c>
+      <c r="C8" s="1">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
       <c r="A9" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>9</v>
+        <v>32</v>
+      </c>
+      <c r="B9" s="1">
+        <v>5</v>
       </c>
       <c r="C9" s="1">
-        <f>AVERAGE(C1:C6)</f>
-        <v>16.5</v>
-      </c>
-      <c r="D9" s="2"/>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B12" s="2">
-        <v>2</v>
-      </c>
-      <c r="C12" s="2">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B13" s="2">
-        <v>2</v>
-      </c>
-      <c r="C13" s="2">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B14" s="2">
-        <v>2</v>
-      </c>
-      <c r="C14" s="2">
-        <v>14</v>
-      </c>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12" s="1">
+        <f>AVERAGE(C1:C9)</f>
+        <v>15.6666666666667</v>
+      </c>
+      <c r="D12" s="2"/>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B15" s="2">
         <v>2</v>
       </c>
       <c r="C15" s="2">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B16" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C16" s="2">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B17" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C17" s="2">
         <v>17</v>
@@ -1579,24 +1663,24 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B18" s="2">
         <v>5</v>
       </c>
       <c r="C18" s="2">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B19" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C19" s="2">
-        <v>21</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1611,19 +1695,19 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C22" s="2">
-        <f>AVERAGE(C12:C19)</f>
-        <v>15.625</v>
+        <f>AVERAGE(C15:C19)</f>
+        <v>14.6</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B25" s="3">
         <v>5</v>
@@ -1644,10 +1728,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="3" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C28" s="3">
         <f>AVERAGE(C25:C25)</f>
@@ -1656,14 +1740,14 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C31" s="4">
-        <f>AVERAGE(C1:C6,C12:C19,C25:C25)</f>
-        <v>16.1333333333333</v>
+        <f>AVERAGE(C1:C9,C15:C19,C25:C25)</f>
+        <v>15.4666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -1696,29 +1780,29 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B2" s="1">
         <v>2</v>
       </c>
       <c r="C2" s="1">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B3" s="1">
         <v>2</v>
       </c>
       <c r="C3" s="1">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B4" s="1">
         <v>2</v>
@@ -1729,165 +1813,165 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B5" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5" s="1">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B6" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C6" s="1">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B7" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C7" s="1">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B8" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C8" s="1">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" s="1">
+        <f>AVERAGE(C2:C8)</f>
+        <v>15.8571428571429</v>
+      </c>
+      <c r="D11" s="2"/>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B14" s="2">
+        <v>4</v>
+      </c>
+      <c r="C14" s="2">
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B9" s="1">
+    <row r="15" spans="1:3">
+      <c r="A15" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B15" s="2">
         <v>4</v>
       </c>
-      <c r="C9" s="1">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B10" s="1">
-        <v>4</v>
-      </c>
-      <c r="C10" s="1">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B11" s="1">
-        <v>4</v>
-      </c>
-      <c r="C11" s="1">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="1">
-        <f>AVERAGE(C2:C11)</f>
-        <v>12.5</v>
-      </c>
-      <c r="D14" s="2"/>
+      <c r="C15" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B16" s="2">
+        <v>5</v>
+      </c>
+      <c r="C16" s="2">
+        <v>13</v>
+      </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="B17" s="2">
+        <v>5</v>
+      </c>
+      <c r="C17" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" s="2">
+        <f>AVERAGE(C14:C17)</f>
+        <v>13.25</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B23" s="3">
+        <v>3</v>
+      </c>
+      <c r="C23" s="3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B24" s="3">
         <v>4</v>
       </c>
-      <c r="C17" s="2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B18" s="2">
-        <v>4</v>
-      </c>
-      <c r="C18" s="2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B19" s="2">
-        <v>4</v>
-      </c>
-      <c r="C19" s="2">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="2"/>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C22" s="2">
-        <f>AVERAGE(C17:C19)</f>
-        <v>13.3333333333333</v>
+      <c r="C24" s="3">
+        <v>15</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="3" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="B25" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C25" s="3">
         <v>12</v>
@@ -1895,7 +1979,7 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="3" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="B26" s="3">
         <v>4</v>
@@ -1916,26 +2000,26 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="3" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C29" s="3">
-        <f>AVERAGE(C25:C26)</f>
-        <v>12</v>
+        <f>AVERAGE(C23:C26)</f>
+        <v>12.75</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C32" s="4">
-        <f>AVERAGE(C2:C11,C17:C19,C25:C26)</f>
-        <v>12.6</v>
+        <f>AVERAGE(C2:C8,C14:C17,C23:C26)</f>
+        <v>14.3333333333333</v>
       </c>
     </row>
   </sheetData>
